--- a/static/excel/ADBE_model.xlsx
+++ b/static/excel/ADBE_model.xlsx
@@ -7339,11 +7339,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>95799.442</v>
+        <v>100079.92</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $237.01</t>
+          <t>FMP marketCap  |  price $247.6</t>
         </is>
       </c>
     </row>
@@ -7425,11 +7425,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0447</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0447</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Damodaran industry unlevered  (Software - Infrastructure)</t>
+          <t>Damodaran industry unlevered  (Software - Application)</t>
         </is>
       </c>
       <c r="B18" s="50" t="n">
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.137</v>
+        <v>1.135</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" s="51" t="n">
-        <v>1.243</v>
+        <v>1.242</v>
       </c>
       <c r="C21" s="49" t="inlineStr">
         <is>
@@ -7715,11 +7715,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.05</v>
+        <v>0.0501</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 0.54%</t>
+          <t>Rf 4.47% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0472</v>
+        <v>0.0473</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>237.01</v>
+        <v>247.6</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10064,7 +10064,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  16 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="D11" s="130" t="inlineStr">
         <is>
-          <t>ROIC trend +22.7% ✓ (≥-2pp)  |  GM maintained +0.9% ✓  |  Op margin +2.0% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.8%/yr ✓ (net buyback)  |  Goodwill/Equity 111% ✗ (&lt;40%)  [4/6 indicators positive — proxy score]</t>
+          <t>ROIC trend +22.7% ✓ (&gt;=-2pp)  |  GM maintained +0.9% ✓  |  Op margin +2.0% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.8%/yr ✓ (net buyback)  |  Goodwill/Equity 111% ✗ (&lt;40%)  [4/6 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E11" s="131" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="H11" s="134" t="inlineStr">
         <is>
-          <t>ROIC trend +22.7% ✓ (≥-2pp)  |  GM maintained +0.9% ✓  |  Op margin +2.0% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.8%/yr ✓ (net buyback)  |  Goodwill/Equity 111% ✗ (&lt;40%)  [4/6 indicators positive — proxy score]</t>
+          <t>ROIC trend +22.7% ✓ (&gt;=-2pp)  |  GM maintained +0.9% ✓  |  Op margin +2.0% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.8%/yr ✓ (net buyback)  |  Goodwill/Equity 111% ✗ (&lt;40%)  [4/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.8x  [-13% vs benchmark]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.7x  [-12% vs benchmark]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.8x  [-13% vs benchmark]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.7x  [-12% vs benchmark]</t>
         </is>
       </c>
     </row>

--- a/static/excel/ADBE_model.xlsx
+++ b/static/excel/ADBE_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7339,11 +7339,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>100079.92</v>
+        <v>98378.238</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $247.6</t>
+          <t>FMP marketCap  |  price $243.39</t>
         </is>
       </c>
     </row>
@@ -7425,11 +7425,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0447</v>
+        <v>0.0467</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-14</t>
+          <t>FRED series DGS10  |  latest: 2026-05-19</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0447</v>
+        <v>0.0467</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.135</v>
+        <v>1.136</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" s="51" t="n">
-        <v>1.242</v>
+        <v>1.243</v>
       </c>
       <c r="C21" s="49" t="inlineStr">
         <is>
@@ -7715,11 +7715,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.0501</v>
+        <v>0.0521</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.47% + spread 0.54%</t>
+          <t>Rf 4.67% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0473</v>
+        <v>0.0483</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>247.6</v>
+        <v>243.39</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10064,7 +10064,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  16 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D9" s="130" t="inlineStr">
         <is>
-          <t>GM 88.6% ✓ (&gt;40%)  |  GM trend +0.9% ✗ (&gt;+1pp)  |  ROIC-WACC +53.7% ✓ (&gt;+5pp)  |  Rev consistency σ=0.5% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
+          <t>GM 88.6% ✓ (&gt;40%)  |  GM trend +0.9% ✗ (&gt;+1pp)  |  ROIC-WACC +47.1% ✓ (&gt;+5pp)  |  Rev consistency σ=0.5% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="131" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="H9" s="134" t="inlineStr">
         <is>
-          <t>GM 88.6% ✓ (&gt;40%)  |  GM trend +0.9% ✗ (&gt;+1pp)  |  ROIC-WACC +53.7% ✓ (&gt;+5pp)  |  Rev consistency σ=0.5% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
+          <t>GM 88.6% ✓ (&gt;40%)  |  GM trend +0.9% ✗ (&gt;+1pp)  |  ROIC-WACC +47.1% ✓ (&gt;+5pp)  |  Rev consistency σ=0.5% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="F14" s="132" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G14" s="133">
         <f>IF(F14="",0,C14*F14*10)</f>
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="F16" s="132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" s="133">
         <f>IF(F16="",0,C16*F16*10)</f>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="F18" s="132" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="133">
         <f>IF(F18="",0,C18*F18*10)</f>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F19" s="132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19" s="133">
         <f>IF(F19="",0,C19*F19*10)</f>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D20" s="130" t="inlineStr">
         <is>
-          <t>Rev growth σ=0.5%  |  Op margin σ=2.0%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=0.5%  |  OM trend -0.1%, σ=2.0%  [quality = direction + stability]</t>
         </is>
       </c>
       <c r="E20" s="136" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="H20" s="134" t="inlineStr">
         <is>
-          <t>Rev growth σ=0.5%  |  Op margin σ=2.0%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=0.5%  |  OM trend -0.1%, σ=2.0%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 19.1x  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.8x  [-12% vs benchmark]</t>
+          <t>Current 19.1x  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.1x [ref only — not used as benchmark]  [-47% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=10.0 → blended 40/40/20=10.00]  PEG≈181.52 (trailing_pe=19.1x / rev_cagr=11%, revenue proxy)</t>
         </is>
       </c>
       <c r="E22" s="136" t="inlineStr">
@@ -10590,7 +10590,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>8.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 19.1x  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.8x  [-12% vs benchmark]</t>
+          <t>Current 19.1x  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.1x [ref only — not used as benchmark]  [-47% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=10.0 → blended 40/40/20=10.00]  PEG≈181.52 (trailing_pe=19.1x / rev_cagr=11%, revenue proxy)</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.7x  [-12% vs benchmark]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.7%  spread=+2.6%→modifier=+0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>8.82</v>
+        <v>10.65</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.7x  [-12% vs benchmark]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.7%  spread=+2.6%→modifier=+0.25]</t>
         </is>
       </c>
     </row>

--- a/static/excel/ADBE_model.xlsx
+++ b/static/excel/ADBE_model.xlsx
@@ -7339,11 +7339,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>98378.238</v>
+        <v>97008</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $243.39</t>
+          <t>FMP marketCap  |  price $240</t>
         </is>
       </c>
     </row>
@@ -7425,11 +7425,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0467</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-19</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0467</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7654,25 +7654,27 @@
       </c>
       <c r="B32" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B33" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7715,11 +7717,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.0521</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.67% + spread 0.54%</t>
+          <t>Rf 4.57% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7745,11 +7747,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0483</v>
+        <v>0.0487</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -7810,16 +7812,16 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B45" s="55">
-        <f>B8*B29+B9*B38*(1-B42)</f>
+        <f>MAX(0.085, B8*B29+B9*B38*(1-B42))</f>
         <v/>
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9450,7 @@
         </is>
       </c>
       <c r="B38" s="101" t="n">
-        <v>15</v>
+        <v>23.3</v>
       </c>
       <c r="C38" s="99" t="n"/>
       <c r="D38" s="99" t="n"/>
@@ -9462,7 +9464,7 @@
       <c r="L38" s="99" t="n"/>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: MEDIUM (10.5% 3yr avg rev growth).  Bear 11x / Base 15x / Bull 19x.  Override manually if needed.</t>
+          <t>Growth tier: MEDIUM (10.5% 3yr avg rev growth).  Bear 17x / Base 23x / Bull 30x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9966,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>243.39</v>
+        <v>240</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10064,7 +10066,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  26 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10583,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 19.1x  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.1x [ref only — not used as benchmark]  [-47% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=10.0 → blended 40/40/20=10.00]  PEG≈181.52 (trailing_pe=19.1x / rev_cagr=11%, revenue proxy)</t>
+          <t>Fwd P/E 10.2x (scoring basis)  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.5x [ref only — not used as benchmark]  [-72% vs benchmark]  [trail=10.00 | fwd_pe=10.2x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=25.13 (fwd_pe=10.2x / eps_growth=41%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="136" t="inlineStr">
@@ -10590,7 +10592,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10598,7 +10600,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 19.1x  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.1x [ref only — not used as benchmark]  [-47% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=10.0 → blended 40/40/20=10.00]  PEG≈181.52 (trailing_pe=19.1x / rev_cagr=11%, revenue proxy)</t>
+          <t>Fwd P/E 10.2x (scoring basis)  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.5x [ref only — not used as benchmark]  [-72% vs benchmark]  [trail=10.00 | fwd_pe=10.2x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=25.13 (fwd_pe=10.2x / eps_growth=41%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10620,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.7%  spread=+2.6%→modifier=+0.25]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.5x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | fwd_pfcf=9.5x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.6%  spread=+2.7%→modifier=+0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10635,7 +10637,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.7%  spread=+2.6%→modifier=+0.25]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.5x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | fwd_pfcf=9.5x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.6%  spread=+2.7%→modifier=+0.25]</t>
         </is>
       </c>
     </row>

--- a/static/excel/ADBE_model.xlsx
+++ b/static/excel/ADBE_model.xlsx
@@ -7339,11 +7339,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>97008</v>
+        <v>97590.048</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $240</t>
+          <t>FMP marketCap  |  price $241.44</t>
         </is>
       </c>
     </row>
@@ -7425,11 +7425,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.043</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: None</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.043</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7666,15 +7666,13 @@
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield  (rating-tier index)</t>
-        </is>
-      </c>
-      <c r="B33" s="46" t="n">
-        <v>0.0507</v>
-      </c>
+          <t>FRED matched yield</t>
+        </is>
+      </c>
+      <c r="B33" s="53" t="n"/>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>FRED BAMLC0A3CAEY — A</t>
+          <t>No rating returned — FRED method not applicable</t>
         </is>
       </c>
     </row>
@@ -7717,11 +7715,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0484</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.54%</t>
+          <t>Rf 4.30% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7747,11 +7745,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0487</v>
+        <v>0.0464</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 3 source(s) above — override freely</t>
+          <t>Default = average of 2 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9964,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>240</v>
+        <v>241.44</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10066,7 +10064,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  26 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — ADBE  |  Master Prompt v2  |  29 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10581,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Fwd P/E 10.2x (scoring basis)  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.5x [ref only — not used as benchmark]  [-72% vs benchmark]  [trail=10.00 | fwd_pe=10.2x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=25.13 (fwd_pe=10.2x / eps_growth=41%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 10.3x (scoring basis)  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 22.3x [ref only — not used as benchmark]  [-75% vs benchmark]  [trail=10.00 | fwd_pe=10.3x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=25.38 (fwd_pe=10.3x / eps_growth=41%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="136" t="inlineStr">
@@ -10600,7 +10598,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Fwd P/E 10.2x (scoring basis)  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 21.5x [ref only — not used as benchmark]  [-72% vs benchmark]  [trail=10.00 | fwd_pe=10.2x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=25.13 (fwd_pe=10.2x / eps_growth=41%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 10.3x (scoring basis)  |  5yr avg 41.4x  |  Sector median 36.3x  |  DCF-implied 22.3x [ref only — not used as benchmark]  [-75% vs benchmark]  [trail=10.00 | fwd_pe=10.3x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=25.38 (fwd_pe=10.3x / eps_growth=41%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10618,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.5x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | fwd_pfcf=9.5x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.6%  spread=+2.7%→modifier=+0.25]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 16.2x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | fwd_pfcf=9.5x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.3%  spread=+2.9%→modifier=+0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10637,7 +10635,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 15.5x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | fwd_pfcf=9.5x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.6%  spread=+2.7%→modifier=+0.25]</t>
+          <t>Current 13.8x  |  5yr avg 29.6x  |  Sector median 51.6x  |  DCF-implied 16.2x [ref only — not used as benchmark]  [-53% vs benchmark]  [trail=10.00 | fwd_pfcf=9.5x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=7.2% vs rf=4.3%  spread=+2.9%→modifier=+0.25]</t>
         </is>
       </c>
     </row>
